--- a/artfynd/A 41080-2026 artfynd.xlsx
+++ b/artfynd/A 41080-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137349970</v>
       </c>
       <c r="B2" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137349984</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137349976</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137349977</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137349983</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137349994</v>
       </c>
       <c r="B7" t="n">
-        <v>92170</v>
+        <v>92173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137349975</v>
       </c>
       <c r="B8" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137349978</v>
       </c>
       <c r="B9" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137349993</v>
       </c>
       <c r="B10" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137349982</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137349998</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>137349986</v>
       </c>
       <c r="B13" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>137349989</v>
       </c>
       <c r="B14" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>137349985</v>
       </c>
       <c r="B15" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>137349988</v>
       </c>
       <c r="B16" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137349980</v>
       </c>
       <c r="B17" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>137349997</v>
       </c>
       <c r="B18" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>137349972</v>
       </c>
       <c r="B19" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>137349996</v>
       </c>
       <c r="B20" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137349971</v>
       </c>
       <c r="B21" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137349992</v>
       </c>
       <c r="B22" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>137349995</v>
       </c>
       <c r="B23" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>137349973</v>
       </c>
       <c r="B24" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>137349974</v>
       </c>
       <c r="B25" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>137349979</v>
       </c>
       <c r="B26" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>137349981</v>
       </c>
       <c r="B27" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>137349990</v>
       </c>
       <c r="B28" t="n">
-        <v>80578</v>
+        <v>80581</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>137349991</v>
       </c>
       <c r="B29" t="n">
-        <v>80578</v>
+        <v>80581</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41080-2026 artfynd.xlsx
+++ b/artfynd/A 41080-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137349970</v>
       </c>
       <c r="B2" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137349984</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137349976</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137349977</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137349983</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137349994</v>
       </c>
       <c r="B7" t="n">
-        <v>92173</v>
+        <v>92175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137349975</v>
       </c>
       <c r="B8" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137349978</v>
       </c>
       <c r="B9" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137349993</v>
       </c>
       <c r="B10" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>137349973</v>
       </c>
       <c r="B24" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>137349974</v>
       </c>
       <c r="B25" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>137349979</v>
       </c>
       <c r="B26" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>137349981</v>
       </c>
       <c r="B27" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 41080-2026 artfynd.xlsx
+++ b/artfynd/A 41080-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137349970</v>
       </c>
       <c r="B2" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137349984</v>
       </c>
       <c r="B3" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137349976</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137349977</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137349983</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137349994</v>
       </c>
       <c r="B7" t="n">
-        <v>92175</v>
+        <v>92180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137349975</v>
       </c>
       <c r="B8" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137349978</v>
       </c>
       <c r="B9" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137349993</v>
       </c>
       <c r="B10" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137349982</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137349998</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>137349986</v>
       </c>
       <c r="B13" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>137349989</v>
       </c>
       <c r="B14" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>137349985</v>
       </c>
       <c r="B15" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>137349988</v>
       </c>
       <c r="B16" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137349980</v>
       </c>
       <c r="B17" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>137349997</v>
       </c>
       <c r="B18" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>137349972</v>
       </c>
       <c r="B19" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>137349996</v>
       </c>
       <c r="B20" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137349971</v>
       </c>
       <c r="B21" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137349992</v>
       </c>
       <c r="B22" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>137349995</v>
       </c>
       <c r="B23" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>137349973</v>
       </c>
       <c r="B24" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>137349974</v>
       </c>
       <c r="B25" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>137349979</v>
       </c>
       <c r="B26" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>137349981</v>
       </c>
       <c r="B27" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>137349990</v>
       </c>
       <c r="B28" t="n">
-        <v>80581</v>
+        <v>80586</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>137349991</v>
       </c>
       <c r="B29" t="n">
-        <v>80581</v>
+        <v>80586</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41080-2026 artfynd.xlsx
+++ b/artfynd/A 41080-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137349970</v>
       </c>
       <c r="B2" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137349984</v>
       </c>
       <c r="B3" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137349976</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137349977</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137349983</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137349994</v>
       </c>
       <c r="B7" t="n">
-        <v>92180</v>
+        <v>92192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137349975</v>
       </c>
       <c r="B8" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137349978</v>
       </c>
       <c r="B9" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137349993</v>
       </c>
       <c r="B10" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137349982</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137349998</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>137349986</v>
       </c>
       <c r="B13" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>137349989</v>
       </c>
       <c r="B14" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>137349985</v>
       </c>
       <c r="B15" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>137349988</v>
       </c>
       <c r="B16" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>137349973</v>
       </c>
       <c r="B24" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>137349974</v>
       </c>
       <c r="B25" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>137349979</v>
       </c>
       <c r="B26" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>137349981</v>
       </c>
       <c r="B27" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>137349990</v>
       </c>
       <c r="B28" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>137349991</v>
       </c>
       <c r="B29" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41080-2026 artfynd.xlsx
+++ b/artfynd/A 41080-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137349970</v>
       </c>
       <c r="B2" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137349984</v>
       </c>
       <c r="B3" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137349976</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137349977</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137349983</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137349994</v>
       </c>
       <c r="B7" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137349975</v>
       </c>
       <c r="B8" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137349978</v>
       </c>
       <c r="B9" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137349993</v>
       </c>
       <c r="B10" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137349982</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137349998</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>137349986</v>
       </c>
       <c r="B13" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>137349989</v>
       </c>
       <c r="B14" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>137349985</v>
       </c>
       <c r="B15" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>137349988</v>
       </c>
       <c r="B16" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>137349973</v>
       </c>
       <c r="B24" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>137349974</v>
       </c>
       <c r="B25" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>137349979</v>
       </c>
       <c r="B26" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>137349981</v>
       </c>
       <c r="B27" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>137349990</v>
       </c>
       <c r="B28" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>137349991</v>
       </c>
       <c r="B29" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41080-2026 artfynd.xlsx
+++ b/artfynd/A 41080-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137349970</v>
       </c>
       <c r="B2" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137349984</v>
       </c>
       <c r="B3" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137349976</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137349977</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137349983</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137349994</v>
       </c>
       <c r="B7" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137349975</v>
       </c>
       <c r="B8" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137349978</v>
       </c>
       <c r="B9" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137349993</v>
       </c>
       <c r="B10" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137349982</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137349998</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>137349986</v>
       </c>
       <c r="B13" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>137349989</v>
       </c>
       <c r="B14" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>137349985</v>
       </c>
       <c r="B15" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>137349988</v>
       </c>
       <c r="B16" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>137349973</v>
       </c>
       <c r="B24" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>137349974</v>
       </c>
       <c r="B25" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>137349979</v>
       </c>
       <c r="B26" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>137349981</v>
       </c>
       <c r="B27" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>137349990</v>
       </c>
       <c r="B28" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>137349991</v>
       </c>
       <c r="B29" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41080-2026 artfynd.xlsx
+++ b/artfynd/A 41080-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137349970</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137349984</v>
       </c>
       <c r="B3" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137349976</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137349977</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137349983</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137349994</v>
       </c>
       <c r="B7" t="n">
-        <v>92196</v>
+        <v>92200</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137349975</v>
       </c>
       <c r="B8" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137349978</v>
       </c>
       <c r="B9" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137349993</v>
       </c>
       <c r="B10" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137349982</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>137349998</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>137349986</v>
       </c>
       <c r="B13" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>137349989</v>
       </c>
       <c r="B14" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>137349985</v>
       </c>
       <c r="B15" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>137349988</v>
       </c>
       <c r="B16" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137349980</v>
       </c>
       <c r="B17" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>137349997</v>
       </c>
       <c r="B18" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>137349972</v>
       </c>
       <c r="B19" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>137349996</v>
       </c>
       <c r="B20" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137349971</v>
       </c>
       <c r="B21" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137349992</v>
       </c>
       <c r="B22" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>137349995</v>
       </c>
       <c r="B23" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>137349973</v>
       </c>
       <c r="B24" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>137349974</v>
       </c>
       <c r="B25" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>137349979</v>
       </c>
       <c r="B26" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>137349981</v>
       </c>
       <c r="B27" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>137349990</v>
       </c>
       <c r="B28" t="n">
-        <v>80600</v>
+        <v>80604</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>137349991</v>
       </c>
       <c r="B29" t="n">
-        <v>80600</v>
+        <v>80604</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
